--- a/modelRecord.xlsx
+++ b/modelRecord.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Research\TerahertzCode\Terahertz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4C2689-E4BD-4EF4-9E26-9A06A644F99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94079E0-2B23-483B-8934-3F63B4FD03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22860" yWindow="1995" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -28,17 +28,129 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Training dataset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>config file name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weighting name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+  <si>
+    <t>Config File Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weighting Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Training Detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Training Dataset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ONN Detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作為baseline，ONN+Restormer的組合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simulation Detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒有加入任何改良</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Performance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Testing Detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Testing Dataset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MNIST 20epochs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Initialization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number of Layers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[0.06, 0.06, 0.06, 0.06]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Random</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>z</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20251013_XXXXXX/baseline_restromer_ONN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Training Loss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Validation Loss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseline_restormer_ONN_padding.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>baseline_restormer_ONN.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20251013_XXXXXX/baseline_restromer_ONN_padding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>padding 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline2_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline2_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做為檢測simulation改良的Baseline2對照組</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -62,12 +174,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -82,8 +212,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -364,26 +521,187 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="46.5703125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" customWidth="1"/>
+    <col min="13" max="13" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="4"/>
+      <c r="M1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>251013</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="L4">
+        <v>3.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <v>251013</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C8" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="F2:H2"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
